--- a/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · El caballero de Olmedo</t>
   </si>
   <si>
-    <t>Para María Isabel Cuena · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para María Isabel Cuena · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>
@@ -207,7 +207,7 @@
     <t>Redondilla · Octosílaba</t>
   </si>
   <si>
-    <t>Sus 225 versos no encajan con «Octosílaba», que se compone de unidades completas de 4 versos. Encajaría con 3 versos más (228) o con 1 verso menos (224).</t>
+    <t>Sus 225 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 3 versos más (228) o con 1 verso menos (224).</t>
   </si>
   <si>
     <t/>
@@ -225,7 +225,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 53 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 53 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>L|6cc5851f-0ef9-41b7-8111-7b49f70b6bae</t>
@@ -234,7 +234,7 @@
     <t>787–885</t>
   </si>
   <si>
-    <t>Tiene 99 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 99 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>L|9655e7f1-89de-4565-9c55-54d9faf77031</t>
@@ -246,7 +246,7 @@
     <t>Seguidilla · Simple</t>
   </si>
   <si>
-    <t>Solo tiene 2 versos, y «Simple» necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
+    <t>Solo tiene 2 versos, y una seguidilla simple necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
   </si>
   <si>
     <t>L|83d7757a-99ef-4653-9fe2-1bcd1cb649af</t>
@@ -1389,10 +1389,10 @@
 hipometrico (276–276)</t>
   </si>
   <si>
-    <t>Revisar: Sus 225 versos no encajan con «Octosílaba», que se compone de unidades completas de 4 versos. Encajaría con 3 versos más (228) o con 1 verso menos (224).</t>
-  </si>
-  <si>
-    <t>Revisar: Tiene 53 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Revisar: Sus 225 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 3 versos más (228) o con 1 verso menos (224).</t>
+  </si>
+  <si>
+    <t>Revisar: Tiene 53 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>461–490</t>
@@ -1427,7 +1427,7 @@
 hipermetrico (878–878)</t>
   </si>
   <si>
-    <t>Revisar: Tiene 99 versos, y un romance no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraremos la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Revisar: Tiene 99 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>seguidilla</t>
@@ -1439,7 +1439,7 @@
     <t>Simple</t>
   </si>
   <si>
-    <t>Revisar: Solo tiene 2 versos, y «Simple» necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
+    <t>Revisar: Solo tiene 2 versos, y una seguidilla simple necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
   </si>
   <si>
     <t xml:space="preserve">hipometrico (961–961)

--- a/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -792,7 +792,7 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
+    <t>Sílabas del verso</t>
   </si>
   <si>
     <t>Sílabas (opcional)</t>
@@ -879,7 +879,7 @@
     <t>D|a6332da3-dfd9-43b0-b85f-8def48d6dba5</t>
   </si>
   <si>
-    <t>Informativa</t>
+    <t>Revisar</t>
   </si>
   <si>
     <t>Soneto · Endecasílabo consonante (503–516)</t>
@@ -4619,7 +4619,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
@@ -6323,17 +6323,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H14">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H10:H53">
       <formula1>Listas!$G$2:$G$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H29">
-      <formula1>Listas!$G$2:$G$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H42">
-      <formula1>Listas!$G$2:$G$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H7">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="H2:H53">
       <formula1>Listas!$G$2:$G$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="509">
   <si>
     <t>Migración métrica · El caballero de Olmedo</t>
   </si>
   <si>
-    <t>Para María Isabel Cuena · generado el 2026-09-20</t>
+    <t>Para María Isabel Cuena · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
@@ -69,12 +69,12 @@
     <t>Abrazada · abba</t>
   </si>
   <si>
+    <t>Tipología 1 · ababa</t>
+  </si>
+  <si>
     <t>a</t>
   </si>
   <si>
-    <t>Tipología 1 · ababa</t>
-  </si>
-  <si>
     <t>Es correcto</t>
   </si>
   <si>
@@ -84,54 +84,54 @@
     <t>Cruzada · abab</t>
   </si>
   <si>
+    <t>Tipología 2 · abbab</t>
+  </si>
+  <si>
     <t>a-a</t>
   </si>
   <si>
-    <t>Tipología 2 · abbab</t>
-  </si>
-  <si>
     <t>No es así (lo corrijo al lado)</t>
   </si>
   <si>
     <t>Es otra cosa (lo explico al lado)</t>
   </si>
   <si>
+    <t>Tipología 3 · abaab</t>
+  </si>
+  <si>
     <t>a-e</t>
   </si>
   <si>
-    <t>Tipología 3 · abaab</t>
+    <t>Tipología 4 · aabab</t>
   </si>
   <si>
     <t>a-o</t>
   </si>
   <si>
-    <t>Tipología 4 · aabab</t>
+    <t>Tipología 5 · aabba</t>
   </si>
   <si>
     <t>e</t>
   </si>
   <si>
-    <t>Tipología 5 · aabba</t>
+    <t>Tipología 6 · abbaa</t>
   </si>
   <si>
     <t>e-a</t>
   </si>
   <si>
-    <t>Tipología 6 · abbaa</t>
+    <t>Tipología 7 · ababb</t>
   </si>
   <si>
     <t>e-e</t>
   </si>
   <si>
-    <t>Tipología 7 · ababb</t>
+    <t>Tipología 8 · abbba</t>
   </si>
   <si>
     <t>e-o</t>
   </si>
   <si>
-    <t>Tipología 8 · abbba</t>
-  </si>
-  <si>
     <t>i</t>
   </si>
   <si>
@@ -207,7 +207,7 @@
     <t>Redondilla · Octosílaba</t>
   </si>
   <si>
-    <t>Sus 225 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 3 versos más (228) o con 1 verso menos (224).</t>
+    <t>Sus 225 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 3 versos más (228) o con 1 verso menos (224). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t/>
@@ -225,7 +225,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 53 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 53 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t>L|6cc5851f-0ef9-41b7-8111-7b49f70b6bae</t>
@@ -234,7 +234,7 @@
     <t>787–885</t>
   </si>
   <si>
-    <t>Tiene 99 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
+    <t>Tiene 99 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
   </si>
   <si>
     <t>L|9655e7f1-89de-4565-9c55-54d9faf77031</t>
@@ -246,7 +246,7 @@
     <t>Seguidilla · Simple</t>
   </si>
   <si>
-    <t>Solo tiene 2 versos, y una seguidilla simple necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma.</t>
+    <t>Solo tiene 2 versos, y una seguidilla simple necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma. Hasta saber esto no te pregunto nada más de este pasaje.</t>
   </si>
   <si>
     <t>L|83d7757a-99ef-4653-9fe2-1bcd1cb649af</t>
@@ -267,12 +267,6 @@
     <t>R|e5e17fde-27d6-462e-a566-93a08eda12b1|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
   </si>
   <si>
-    <t>Esquema de rima · 56 estrofas</t>
-  </si>
-  <si>
-    <t>R|8b0e77d1-19b4-492a-a7b4-46380f9e0a9e|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
     <t>491–502</t>
   </si>
   <si>
@@ -309,174 +303,171 @@
     <t>R|df1e0910-ed8d-4e2f-8751-e48500f0d23f|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
   </si>
   <si>
+    <t>888–1035</t>
+  </si>
+  <si>
+    <t>Esquema de rima · 37 estrofas</t>
+  </si>
+  <si>
+    <t>R|df4d4d5a-6347-4d0c-a377-8677a0c13748|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
+    <t>1096–1103</t>
+  </si>
+  <si>
+    <t>Esquema de rima · 2 estrofas</t>
+  </si>
+  <si>
+    <t>R|fa6b18e9-b7f4-4a77-9ef6-fcbba0f96a9d|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
+    <t>1109–1112</t>
+  </si>
+  <si>
+    <t>Esquema de rima · 1 estrofa</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable</t>
+  </si>
+  <si>
+    <t>R|385cee66-54b1-408c-a01b-12559ab347b0|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
+    <t>1113–1162</t>
+  </si>
+  <si>
+    <t>Copla real · Octosílaba consonante</t>
+  </si>
+  <si>
+    <t>Primera quintilla · Esquema de rima · copla real 1 (vv. 1113–1122)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1113</t>
+  </si>
+  <si>
+    <t>Primera quintilla · Esquema de rima · copla real 2 (vv. 1123–1132)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1123</t>
+  </si>
+  <si>
+    <t>Primera quintilla · Esquema de rima · copla real 3 (vv. 1133–1142)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1133</t>
+  </si>
+  <si>
+    <t>Primera quintilla · Esquema de rima · copla real 4 (vv. 1143–1152)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1143</t>
+  </si>
+  <si>
+    <t>Primera quintilla · Esquema de rima · copla real 5 (vv. 1153–1162)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1153</t>
+  </si>
+  <si>
+    <t>Segunda quintilla · Esquema de rima · copla real 1 (vv. 1113–1122)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1113</t>
+  </si>
+  <si>
+    <t>Segunda quintilla · Esquema de rima · copla real 2 (vv. 1123–1132)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1123</t>
+  </si>
+  <si>
+    <t>Segunda quintilla · Esquema de rima · copla real 3 (vv. 1133–1142)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1133</t>
+  </si>
+  <si>
+    <t>Segunda quintilla · Esquema de rima · copla real 4 (vv. 1143–1152)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1143</t>
+  </si>
+  <si>
+    <t>Segunda quintilla · Esquema de rima · copla real 5 (vv. 1153–1162)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1153</t>
+  </si>
+  <si>
+    <t>Pie quebrado · estrofa 1 (vv. 1113–1122)</t>
+  </si>
+  <si>
+    <t>Indica en qué versos cae el quebrado y cuántas sílabas tiene cada uno («3: 4, 8: 5»)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1113</t>
+  </si>
+  <si>
+    <t>Pie quebrado · estrofa 2 (vv. 1123–1132)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1123</t>
+  </si>
+  <si>
+    <t>Pie quebrado · estrofa 3 (vv. 1133–1142)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1133</t>
+  </si>
+  <si>
+    <t>Pie quebrado · estrofa 4 (vv. 1143–1152)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1143</t>
+  </si>
+  <si>
+    <t>Pie quebrado · estrofa 5 (vv. 1153–1162)</t>
+  </si>
+  <si>
+    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1153</t>
+  </si>
+  <si>
+    <t>1163–1250</t>
+  </si>
+  <si>
+    <t>Esquema de rima · 22 estrofas</t>
+  </si>
+  <si>
+    <t>R|a91a6373-594c-4ff7-b0ec-bb39420bcb61|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
+    <t>1394–1465</t>
+  </si>
+  <si>
+    <t>Esquema de rima · 18 estrofas</t>
+  </si>
+  <si>
+    <t>R|7c3055a5-c847-45e2-9943-4e087adb6c0f|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
+    <t>1554–1609</t>
+  </si>
+  <si>
+    <t>Esquema de rima · 14 estrofas</t>
+  </si>
+  <si>
+    <t>R|bf624684-5c51-4f71-8c6a-583eafcd37fd|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
+    <t>1610–1659</t>
+  </si>
+  <si>
+    <t>Romancillo · Heptasílabo</t>
+  </si>
+  <si>
     <t>Vocales de la asonancia</t>
   </si>
   <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>R|83d7757a-99ef-4653-9fe2-1bcd1cb649af|bdf7ff3a-537b-4108-b636-f925128f93b0</t>
-  </si>
-  <si>
-    <t>888–1035</t>
-  </si>
-  <si>
-    <t>Esquema de rima · 37 estrofas</t>
-  </si>
-  <si>
-    <t>R|df4d4d5a-6347-4d0c-a377-8677a0c13748|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>1096–1103</t>
-  </si>
-  <si>
-    <t>Esquema de rima · 2 estrofas</t>
-  </si>
-  <si>
-    <t>R|fa6b18e9-b7f4-4a77-9ef6-fcbba0f96a9d|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>1109–1112</t>
-  </si>
-  <si>
-    <t>Esquema de rima · 1 estrofa</t>
-  </si>
-  <si>
-    <t>R|385cee66-54b1-408c-a01b-12559ab347b0|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>1113–1162</t>
-  </si>
-  <si>
-    <t>Copla real · Octosílaba consonante</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 1 (vv. 1113–1122)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1113</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 2 (vv. 1123–1132)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1123</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 3 (vv. 1133–1142)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1133</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 4 (vv. 1143–1152)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1143</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 5 (vv. 1153–1162)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1153</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 1 (vv. 1113–1122)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1113</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 2 (vv. 1123–1132)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1123</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 3 (vv. 1133–1142)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1133</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 4 (vv. 1143–1152)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1143</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 5 (vv. 1153–1162)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1153</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 1 (vv. 1113–1122)</t>
-  </si>
-  <si>
-    <t>Indica en qué versos cae el quebrado y cuántas sílabas tiene cada uno («3: 4, 8: 5»)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1113</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 2 (vv. 1123–1132)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1123</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 3 (vv. 1133–1142)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1133</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 4 (vv. 1143–1152)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1143</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 5 (vv. 1153–1162)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1153</t>
-  </si>
-  <si>
-    <t>1163–1250</t>
-  </si>
-  <si>
-    <t>Esquema de rima · 22 estrofas</t>
-  </si>
-  <si>
-    <t>R|a91a6373-594c-4ff7-b0ec-bb39420bcb61|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>1394–1465</t>
-  </si>
-  <si>
-    <t>Esquema de rima · 18 estrofas</t>
-  </si>
-  <si>
-    <t>R|7c3055a5-c847-45e2-9943-4e087adb6c0f|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>1554–1609</t>
-  </si>
-  <si>
-    <t>Esquema de rima · 14 estrofas</t>
-  </si>
-  <si>
-    <t>R|bf624684-5c51-4f71-8c6a-583eafcd37fd|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
-  </si>
-  <si>
-    <t>1610–1659</t>
-  </si>
-  <si>
-    <t>Romancillo · Heptasílabo</t>
-  </si>
-  <si>
     <t>R|3376b77f-7fc0-480e-8e4f-3bea02d6ae4f|9f9dae10-f71b-4761-8f0f-fb3fb2fbd71a</t>
   </si>
   <si>
@@ -510,61 +501,61 @@
     <t>2178–2227</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 1 (vv. 2178–2187)</t>
+    <t>Primera quintilla · Esquema de rima · copla real 1 (vv. 2178–2187)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2178</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 2 (vv. 2188–2197)</t>
+    <t>Primera quintilla · Esquema de rima · copla real 2 (vv. 2188–2197)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2188</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 3 (vv. 2198–2207)</t>
+    <t>Primera quintilla · Esquema de rima · copla real 3 (vv. 2198–2207)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2198</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 4 (vv. 2208–2217)</t>
+    <t>Primera quintilla · Esquema de rima · copla real 4 (vv. 2208–2217)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2208</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 5 (vv. 2218–2227)</t>
+    <t>Primera quintilla · Esquema de rima · copla real 5 (vv. 2218–2227)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2218</t>
   </si>
   <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 1 (vv. 2178–2187)</t>
+    <t>Segunda quintilla · Esquema de rima · copla real 1 (vv. 2178–2187)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2178</t>
   </si>
   <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 2 (vv. 2188–2197)</t>
+    <t>Segunda quintilla · Esquema de rima · copla real 2 (vv. 2188–2197)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2188</t>
   </si>
   <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 3 (vv. 2198–2207)</t>
+    <t>Segunda quintilla · Esquema de rima · copla real 3 (vv. 2198–2207)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2198</t>
   </si>
   <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 4 (vv. 2208–2217)</t>
+    <t>Segunda quintilla · Esquema de rima · copla real 4 (vv. 2208–2217)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2208</t>
   </si>
   <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 5 (vv. 2218–2227)</t>
+    <t>Segunda quintilla · Esquema de rima · copla real 5 (vv. 2218–2227)</t>
   </si>
   <si>
     <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2218</t>
@@ -582,13 +573,13 @@
     <t>2364–2373</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · estrofa 1 (vv. 2364–2373)</t>
+    <t>Primera quintilla · Esquema de rima · copla real 1 (vv. 2364–2373)</t>
   </si>
   <si>
     <t>U|233c1cc1-8d46-4486-b32d-3c9cb395e604|7d6da838-573a-4d7f-a38b-ddcff61173cc|2364</t>
   </si>
   <si>
-    <t>Segunda quintilla · Esquema de rima · estrofa 1 (vv. 2364–2373)</t>
+    <t>Segunda quintilla · Esquema de rima · copla real 1 (vv. 2364–2373)</t>
   </si>
   <si>
     <t>U|233c1cc1-8d46-4486-b32d-3c9cb395e604|73d6744a-81e5-478f-8b98-0444f007919a|2364</t>
@@ -1114,6 +1105,9 @@
   </si>
   <si>
     <t>1355–1366</t>
+  </si>
+  <si>
+    <t>Pasa a ser una desviación de rima</t>
   </si>
   <si>
     <t>D|843764e2-2ae5-4e62-90d6-4ce78823df2f</t>
@@ -2208,63 +2202,63 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E10" t="s">
+    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E11" t="s">
+    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E12" t="s">
+    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E13" t="s">
+    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E14" t="s">
+    <row r="14" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E15" t="s">
+    <row r="15" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E16" t="s">
+    <row r="16" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" t="s">
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" t="s">
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" t="s">
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" t="s">
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" t="s">
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2276,7 +2270,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -2487,13 +2481,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>64</v>
@@ -2511,7 +2505,7 @@
         <v>64</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2519,13 +2513,13 @@
         <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>64</v>
@@ -2543,7 +2537,7 @@
         <v>64</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2551,13 +2545,13 @@
         <v>78</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>64</v>
@@ -2575,7 +2569,7 @@
         <v>64</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2583,13 +2577,13 @@
         <v>78</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>64</v>
@@ -2607,7 +2601,7 @@
         <v>64</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2615,13 +2609,13 @@
         <v>78</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>64</v>
@@ -2639,7 +2633,7 @@
         <v>64</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2647,19 +2641,19 @@
         <v>78</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>64</v>
@@ -2671,7 +2665,7 @@
         <v>64</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2679,19 +2673,19 @@
         <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>64</v>
@@ -2703,7 +2697,7 @@
         <v>64</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2711,20 +2705,20 @@
         <v>78</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="G14" s="6" t="s">
         <v>64</v>
       </c>
@@ -2735,7 +2729,7 @@
         <v>64</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2743,19 +2737,19 @@
         <v>78</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>64</v>
@@ -2767,7 +2761,7 @@
         <v>64</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2775,10 +2769,10 @@
         <v>78</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>111</v>
@@ -2787,7 +2781,7 @@
         <v>64</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>64</v>
@@ -2807,10 +2801,10 @@
         <v>78</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>113</v>
@@ -2819,7 +2813,7 @@
         <v>64</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>64</v>
@@ -2839,10 +2833,10 @@
         <v>78</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>115</v>
@@ -2851,7 +2845,7 @@
         <v>64</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>64</v>
@@ -2871,10 +2865,10 @@
         <v>78</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>117</v>
@@ -2883,7 +2877,7 @@
         <v>64</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>64</v>
@@ -2903,10 +2897,10 @@
         <v>78</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>119</v>
@@ -2915,7 +2909,7 @@
         <v>64</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>64</v>
@@ -2935,10 +2929,10 @@
         <v>78</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>121</v>
@@ -2947,7 +2941,7 @@
         <v>64</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>64</v>
@@ -2967,10 +2961,10 @@
         <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>123</v>
@@ -2979,7 +2973,7 @@
         <v>64</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>64</v>
@@ -2999,10 +2993,10 @@
         <v>78</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>125</v>
@@ -3011,7 +3005,7 @@
         <v>64</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>64</v>
@@ -3031,10 +3025,10 @@
         <v>78</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>127</v>
@@ -3043,7 +3037,7 @@
         <v>64</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>64</v>
@@ -3055,7 +3049,7 @@
         <v>64</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3063,19 +3057,19 @@
         <v>78</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>64</v>
@@ -3087,7 +3081,7 @@
         <v>64</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3095,19 +3089,19 @@
         <v>78</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>64</v>
@@ -3127,10 +3121,10 @@
         <v>78</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>134</v>
@@ -3139,7 +3133,7 @@
         <v>64</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>64</v>
@@ -3159,10 +3153,10 @@
         <v>78</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>136</v>
@@ -3171,7 +3165,7 @@
         <v>64</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>64</v>
@@ -3191,19 +3185,19 @@
         <v>78</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>64</v>
@@ -3215,7 +3209,7 @@
         <v>64</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3223,19 +3217,19 @@
         <v>78</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>64</v>
@@ -3247,7 +3241,7 @@
         <v>64</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3255,13 +3249,13 @@
         <v>78</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>64</v>
@@ -3279,7 +3273,7 @@
         <v>64</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3287,19 +3281,19 @@
         <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>64</v>
@@ -3311,7 +3305,7 @@
         <v>64</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3319,13 +3313,13 @@
         <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>64</v>
@@ -3343,7 +3337,7 @@
         <v>64</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3351,19 +3345,19 @@
         <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>64</v>
@@ -3375,7 +3369,7 @@
         <v>64</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3383,13 +3377,13 @@
         <v>78</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>64</v>
@@ -3407,7 +3401,7 @@
         <v>64</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3415,19 +3409,19 @@
         <v>78</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>64</v>
@@ -3439,7 +3433,7 @@
         <v>64</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3450,16 +3444,16 @@
         <v>160</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>64</v>
@@ -3471,7 +3465,7 @@
         <v>64</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3479,19 +3473,19 @@
         <v>78</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>64</v>
@@ -3503,7 +3497,7 @@
         <v>64</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3511,19 +3505,19 @@
         <v>78</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>64</v>
@@ -3535,7 +3529,7 @@
         <v>64</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3543,19 +3537,19 @@
         <v>78</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>64</v>
@@ -3567,7 +3561,7 @@
         <v>64</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3575,19 +3569,19 @@
         <v>78</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>64</v>
@@ -3599,7 +3593,7 @@
         <v>64</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3607,19 +3601,19 @@
         <v>78</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>64</v>
@@ -3631,7 +3625,7 @@
         <v>64</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3639,19 +3633,19 @@
         <v>78</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>64</v>
@@ -3663,7 +3657,7 @@
         <v>64</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3671,19 +3665,19 @@
         <v>78</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>64</v>
@@ -3695,7 +3689,7 @@
         <v>64</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3703,19 +3697,19 @@
         <v>78</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>64</v>
@@ -3727,7 +3721,7 @@
         <v>64</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3735,19 +3729,19 @@
         <v>78</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>64</v>
@@ -3759,7 +3753,7 @@
         <v>64</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3767,19 +3761,19 @@
         <v>78</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>64</v>
@@ -3791,7 +3785,7 @@
         <v>64</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3802,16 +3796,16 @@
         <v>184</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>64</v>
@@ -3823,7 +3817,7 @@
         <v>64</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3831,19 +3825,19 @@
         <v>78</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>64</v>
@@ -3855,7 +3849,7 @@
         <v>64</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3863,19 +3857,19 @@
         <v>78</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>64</v>
@@ -3887,7 +3881,7 @@
         <v>64</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3895,19 +3889,19 @@
         <v>78</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>64</v>
@@ -3919,7 +3913,7 @@
         <v>64</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3927,13 +3921,13 @@
         <v>78</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>64</v>
@@ -3951,7 +3945,7 @@
         <v>64</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3959,19 +3953,19 @@
         <v>78</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>197</v>
+        <v>62</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>64</v>
@@ -3983,128 +3977,58 @@
         <v>64</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="18">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G11">
+  <dataValidations count="16">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G13">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G12">
-      <formula1>Listas!$E$2:$E$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G13:G15">
-      <formula1>Listas!$D$2:$D$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G16:G25">
-      <formula1>Listas!$F$2:$F$9</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G14:G23">
+      <formula1>Listas!$E$2:$E$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G29:G31">
+      <formula1>Listas!$D$2:$D$3</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G3:G4">
       <formula1>Listas!$B$2:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G31:G33">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G32">
+      <formula1>Listas!$F$2:$F$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G33:G35">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G34">
-      <formula1>Listas!$E$2:$E$21</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G36:G45">
+      <formula1>Listas!$E$2:$E$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G35:G37">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G46">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G38:G47">
-      <formula1>Listas!$F$2:$F$9</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G47:G48">
+      <formula1>Listas!$E$2:$E$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G48">
-      <formula1>Listas!$D$2:$D$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G49:G50">
-      <formula1>Listas!$F$2:$F$9</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G49">
+      <formula1>Listas!$F$2:$F$21</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5">
       <formula1>Listas!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G51">
-      <formula1>Listas!$E$2:$E$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G52">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G50">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G53">
-      <formula1>Listas!$E$2:$E$21</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G51">
+      <formula1>Listas!$F$2:$F$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G54:G55">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G52:G53">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G6:G11">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G6:G13">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -4137,19 +4061,19 @@
         <v>52</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>58</v>
@@ -4160,19 +4084,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>64</v>
@@ -4184,7 +4108,7 @@
         <v>64</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4195,13 +4119,13 @@
         <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>64</v>
@@ -4213,53 +4137,53 @@
         <v>64</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>214</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>64</v>
@@ -4271,24 +4195,24 @@
         <v>64</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>64</v>
@@ -4300,7 +4224,7 @@
         <v>64</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4311,13 +4235,13 @@
         <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>64</v>
@@ -4329,24 +4253,24 @@
         <v>64</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>64</v>
@@ -4358,53 +4282,53 @@
         <v>64</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>64</v>
@@ -4416,24 +4340,24 @@
         <v>64</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>64</v>
@@ -4445,24 +4369,24 @@
         <v>64</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>64</v>
@@ -4474,24 +4398,24 @@
         <v>64</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>64</v>
@@ -4503,53 +4427,53 @@
         <v>64</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="F14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>64</v>
@@ -4561,24 +4485,24 @@
         <v>64</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>64</v>
@@ -4590,7 +4514,7 @@
         <v>64</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -4633,22 +4557,22 @@
         <v>51</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>258</v>
-      </c>
       <c r="H1" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>58</v>
@@ -4659,87 +4583,87 @@
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="G2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>261</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>267</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="G4" s="6" t="s">
         <v>64</v>
       </c>
@@ -4750,28 +4674,28 @@
         <v>64</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="G5" s="6" t="s">
         <v>64</v>
       </c>
@@ -4782,27 +4706,27 @@
         <v>64</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>64</v>
@@ -4814,155 +4738,155 @@
         <v>64</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="G7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>283</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="G8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>293</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>64</v>
@@ -4974,59 +4898,59 @@
         <v>64</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>304</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>64</v>
@@ -5038,59 +4962,59 @@
         <v>64</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>311</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>64</v>
@@ -5102,27 +5026,27 @@
         <v>64</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>64</v>
@@ -5134,27 +5058,27 @@
         <v>64</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>64</v>
@@ -5166,59 +5090,59 @@
         <v>64</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>324</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>64</v>
@@ -5230,187 +5154,187 @@
         <v>64</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>331</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>335</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>339</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>343</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>347</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>64</v>
@@ -5422,27 +5346,27 @@
         <v>64</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>64</v>
@@ -5454,91 +5378,91 @@
         <v>64</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="E27" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>361</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="E29" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>285</v>
+        <v>363</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>64</v>
@@ -5550,283 +5474,283 @@
         <v>64</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>367</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J31" s="7" t="s">
         <v>370</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>374</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J33" s="7" t="s">
         <v>377</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" s="7" t="s">
         <v>380</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="F35" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>384</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>387</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="E37" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>390</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>64</v>
@@ -5838,27 +5762,27 @@
         <v>64</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>64</v>
@@ -5870,59 +5794,59 @@
         <v>64</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="E40" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J40" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>64</v>
@@ -5934,187 +5858,187 @@
         <v>64</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="F42" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J42" s="7" t="s">
         <v>403</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J43" s="7" t="s">
         <v>406</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="E44" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J44" s="7" t="s">
         <v>409</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J45" s="7" t="s">
         <v>412</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="E46" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J46" s="7" t="s">
         <v>415</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>64</v>
@@ -6126,27 +6050,27 @@
         <v>64</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>64</v>
@@ -6158,27 +6082,27 @@
         <v>64</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>64</v>
@@ -6190,59 +6114,59 @@
         <v>64</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J50" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>64</v>
@@ -6254,59 +6178,59 @@
         <v>64</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J52" s="7" t="s">
         <v>429</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>64</v>
@@ -6318,7 +6242,7 @@
         <v>64</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -6356,37 +6280,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>437</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>439</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>54</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6394,34 +6318,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C2" s="3">
         <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>444</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6435,28 +6359,28 @@
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6464,34 +6388,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C4" s="3">
         <v>108</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6505,28 +6429,28 @@
         <v>225</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6540,28 +6464,28 @@
         <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="K6" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6569,34 +6493,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C7" s="3">
         <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>444</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6604,34 +6528,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="3">
         <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6639,34 +6563,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C9" s="3">
         <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6674,34 +6598,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3">
         <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6709,34 +6633,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C11" s="3">
         <v>38</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6744,34 +6668,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C12" s="3">
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6779,34 +6703,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C13" s="3">
         <v>84</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6814,34 +6738,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C14" s="3">
         <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6855,28 +6779,28 @@
         <v>99</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6890,28 +6814,28 @@
         <v>2</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>471</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6919,34 +6843,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3">
         <v>148</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6954,34 +6878,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C18" s="3">
         <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>444</v>
-      </c>
       <c r="G18" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6989,34 +6913,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C19" s="3">
         <v>8</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7024,34 +6948,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C20" s="3">
         <v>5</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>481</v>
-      </c>
       <c r="K20" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7059,34 +6983,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C21" s="3">
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7094,34 +7018,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C22" s="3">
         <v>50</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="J22" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7129,34 +7053,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C23" s="3">
         <v>88</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7164,34 +7088,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C24" s="3">
         <v>82</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7199,34 +7123,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C25" s="3">
         <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>488</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>490</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7234,34 +7158,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C26" s="3">
         <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7269,34 +7193,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C27" s="3">
         <v>88</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7304,34 +7228,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C28" s="3">
         <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7339,34 +7263,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C29" s="3">
         <v>50</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>497</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7374,34 +7298,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C30" s="3">
         <v>68</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7409,34 +7333,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C31" s="3">
         <v>86</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7444,34 +7368,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C32" s="3">
         <v>200</v>
       </c>
       <c r="D32" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7479,34 +7403,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C33" s="3">
         <v>64</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7514,34 +7438,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C34" s="3">
         <v>100</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7549,34 +7473,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C35" s="3">
         <v>50</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7584,34 +7508,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C36" s="3">
         <v>24</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7619,34 +7543,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C37" s="3">
         <v>52</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7654,34 +7578,34 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C38" s="3">
         <v>40</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7689,34 +7613,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C39" s="3">
         <v>20</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>444</v>
-      </c>
       <c r="G39" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7724,34 +7648,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C40" s="3">
         <v>10</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7759,34 +7683,34 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C41" s="3">
         <v>4</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>470</v>
-      </c>
       <c r="G41" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7794,34 +7718,34 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C42" s="3">
         <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="G42" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7829,34 +7753,34 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C43" s="3">
         <v>7</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7864,34 +7788,34 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C44" s="3">
         <v>24</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="G44" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7899,34 +7823,34 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C45" s="3">
         <v>92</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7934,34 +7858,34 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C46" s="3">
         <v>80</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="G46" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J46" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7969,34 +7893,34 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C47" s="3">
         <v>144</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="513">
   <si>
     <t>Migración métrica · El caballero de Olmedo</t>
   </si>
@@ -69,12 +69,12 @@
     <t>Abrazada · abba</t>
   </si>
   <si>
+    <t>a</t>
+  </si>
+  <si>
     <t>Tipología 1 · ababa</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
     <t>Es correcto</t>
   </si>
   <si>
@@ -84,54 +84,54 @@
     <t>Cruzada · abab</t>
   </si>
   <si>
+    <t>a-a</t>
+  </si>
+  <si>
     <t>Tipología 2 · abbab</t>
   </si>
   <si>
-    <t>a-a</t>
-  </si>
-  <si>
     <t>No es así (lo corrijo al lado)</t>
   </si>
   <si>
     <t>Es otra cosa (lo explico al lado)</t>
   </si>
   <si>
+    <t>a-e</t>
+  </si>
+  <si>
     <t>Tipología 3 · abaab</t>
   </si>
   <si>
-    <t>a-e</t>
+    <t>a-o</t>
   </si>
   <si>
     <t>Tipología 4 · aabab</t>
   </si>
   <si>
-    <t>a-o</t>
+    <t>e</t>
   </si>
   <si>
     <t>Tipología 5 · aabba</t>
   </si>
   <si>
-    <t>e</t>
+    <t>e-a</t>
   </si>
   <si>
     <t>Tipología 6 · abbaa</t>
   </si>
   <si>
-    <t>e-a</t>
+    <t>e-e</t>
   </si>
   <si>
     <t>Tipología 7 · ababb</t>
   </si>
   <si>
-    <t>e-e</t>
+    <t>e-o</t>
   </si>
   <si>
     <t>Tipología 8 · abbba</t>
   </si>
   <si>
-    <t>e-o</t>
-  </si>
-  <si>
     <t>i</t>
   </si>
   <si>
@@ -207,7 +207,7 @@
     <t>Redondilla · Octosílaba</t>
   </si>
   <si>
-    <t>Sus 225 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 3 versos más (228) o con 1 verso menos (224). Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Sus 225 versos no encajan en una redondilla octosílaba, que se compone de unidades completas de 4 versos. Encajaría con 3 versos más (228) o con 1 verso menos (224). Lo demás que te pregunto de este pasaje va contestado de una vez para todas sus estrofas, así que la respuesta vale igual si el rango cambia.</t>
   </si>
   <si>
     <t/>
@@ -225,7 +225,7 @@
     <t>Romance · Octosílabo</t>
   </si>
   <si>
-    <t>Tiene 53 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Tiene 53 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>L|6cc5851f-0ef9-41b7-8111-7b49f70b6bae</t>
@@ -234,7 +234,7 @@
     <t>787–885</t>
   </si>
   <si>
-    <t>Tiene 99 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto. Las preguntas que dependen de cómo se reparta en estrofas te las haré cuando esto esté claro.</t>
+    <t>Tiene 99 versos, y un romance octosílabo no puede tener un número impar: en algún punto falta o sobra un verso. Hay que localizarlo y decir si se trata de una laguna, en cuyo caso renumeraré la obra a partir de ahí, o de un error en el rango, en cuyo caso hace falta el rango correcto.</t>
   </si>
   <si>
     <t>L|9655e7f1-89de-4565-9c55-54d9faf77031</t>
@@ -246,7 +246,7 @@
     <t>Seguidilla · Simple</t>
   </si>
   <si>
-    <t>Solo tiene 2 versos, y una seguidilla simple necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma. Hasta saber esto no te pregunto nada más de este pasaje.</t>
+    <t>Solo tiene 2 versos, y una seguidilla simple necesita al menos 4. Puede que el rango esté mal o que se trate de otra forma. Lo demás que te pregunto de este pasaje va contestado de una vez para todas sus estrofas, así que la respuesta vale igual si el rango cambia.</t>
   </si>
   <si>
     <t>L|83d7757a-99ef-4653-9fe2-1bcd1cb649af</t>
@@ -267,6 +267,15 @@
     <t>R|e5e17fde-27d6-462e-a566-93a08eda12b1|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
   </si>
   <si>
+    <t>Esquema de rima · todas las estrofas</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta). Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+  </si>
+  <si>
+    <t>R|8b0e77d1-19b4-492a-a7b4-46380f9e0a9e|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
+  </si>
+  <si>
     <t>491–502</t>
   </si>
   <si>
@@ -303,6 +312,15 @@
     <t>R|df1e0910-ed8d-4e2f-8751-e48500f0d23f|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
   </si>
   <si>
+    <t>Vocales de la asonancia</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable</t>
+  </si>
+  <si>
+    <t>R|83d7757a-99ef-4653-9fe2-1bcd1cb649af|bdf7ff3a-537b-4108-b636-f925128f93b0</t>
+  </si>
+  <si>
     <t>888–1035</t>
   </si>
   <si>
@@ -327,9 +345,6 @@
     <t>Esquema de rima · 1 estrofa</t>
   </si>
   <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
     <t>R|385cee66-54b1-408c-a01b-12559ab347b0|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
   </si>
   <si>
@@ -463,9 +478,6 @@
   </si>
   <si>
     <t>Romancillo · Heptasílabo</t>
-  </si>
-  <si>
-    <t>Vocales de la asonancia</t>
   </si>
   <si>
     <t>R|3376b77f-7fc0-480e-8e4f-3bea02d6ae4f|9f9dae10-f71b-4761-8f0f-fb3fb2fbd71a</t>
@@ -2202,63 +2214,63 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F10" t="s">
+    <row r="10" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F11" t="s">
+    <row r="11" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
+    <row r="12" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F13" t="s">
+    <row r="13" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F14" t="s">
+    <row r="14" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F15" t="s">
+    <row r="15" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F16" t="s">
+    <row r="16" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F17" t="s">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F18" t="s">
+    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F19" t="s">
+    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F20" t="s">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F21" t="s">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2270,7 +2282,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -2481,19 +2493,19 @@
         <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>64</v>
@@ -2641,19 +2653,19 @@
         <v>78</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>64</v>
@@ -2685,19 +2697,19 @@
         <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2705,31 +2717,31 @@
         <v>78</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2737,31 +2749,31 @@
         <v>78</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2769,19 +2781,19 @@
         <v>78</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>64</v>
@@ -2793,7 +2805,7 @@
         <v>64</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2801,19 +2813,19 @@
         <v>78</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>64</v>
@@ -2825,7 +2837,7 @@
         <v>64</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2833,19 +2845,19 @@
         <v>78</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>64</v>
@@ -2857,7 +2869,7 @@
         <v>64</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2865,19 +2877,19 @@
         <v>78</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>64</v>
@@ -2889,7 +2901,7 @@
         <v>64</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2897,19 +2909,19 @@
         <v>78</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>64</v>
@@ -2921,7 +2933,7 @@
         <v>64</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2929,19 +2941,19 @@
         <v>78</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>64</v>
@@ -2953,7 +2965,7 @@
         <v>64</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2961,19 +2973,19 @@
         <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>64</v>
@@ -2985,7 +2997,7 @@
         <v>64</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2993,19 +3005,19 @@
         <v>78</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>64</v>
@@ -3017,7 +3029,7 @@
         <v>64</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3025,19 +3037,19 @@
         <v>78</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>64</v>
@@ -3057,10 +3069,10 @@
         <v>78</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>130</v>
@@ -3069,7 +3081,7 @@
         <v>64</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>64</v>
@@ -3089,10 +3101,10 @@
         <v>78</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>132</v>
@@ -3101,7 +3113,7 @@
         <v>64</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>64</v>
@@ -3113,7 +3125,7 @@
         <v>64</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3121,19 +3133,19 @@
         <v>78</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>64</v>
@@ -3145,7 +3157,7 @@
         <v>64</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3153,19 +3165,19 @@
         <v>78</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>64</v>
@@ -3177,7 +3189,7 @@
         <v>64</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3185,10 +3197,10 @@
         <v>78</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>139</v>
@@ -3197,7 +3209,7 @@
         <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>64</v>
@@ -3217,31 +3229,31 @@
         <v>78</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3249,13 +3261,13 @@
         <v>78</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>64</v>
@@ -3273,7 +3285,7 @@
         <v>64</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3281,31 +3293,31 @@
         <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3313,13 +3325,13 @@
         <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>64</v>
@@ -3337,7 +3349,7 @@
         <v>64</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3345,31 +3357,31 @@
         <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3377,13 +3389,13 @@
         <v>78</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>64</v>
@@ -3401,7 +3413,7 @@
         <v>64</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3409,31 +3421,31 @@
         <v>78</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>160</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3441,31 +3453,31 @@
         <v>78</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3473,10 +3485,10 @@
         <v>78</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>165</v>
@@ -3485,7 +3497,7 @@
         <v>64</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>64</v>
@@ -3505,10 +3517,10 @@
         <v>78</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>167</v>
@@ -3517,7 +3529,7 @@
         <v>64</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>64</v>
@@ -3537,10 +3549,10 @@
         <v>78</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>169</v>
@@ -3549,7 +3561,7 @@
         <v>64</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>64</v>
@@ -3569,10 +3581,10 @@
         <v>78</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>171</v>
@@ -3581,7 +3593,7 @@
         <v>64</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>64</v>
@@ -3601,10 +3613,10 @@
         <v>78</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>173</v>
@@ -3613,7 +3625,7 @@
         <v>64</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>64</v>
@@ -3633,10 +3645,10 @@
         <v>78</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>175</v>
@@ -3645,7 +3657,7 @@
         <v>64</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>64</v>
@@ -3665,10 +3677,10 @@
         <v>78</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>177</v>
@@ -3677,7 +3689,7 @@
         <v>64</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>64</v>
@@ -3697,10 +3709,10 @@
         <v>78</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>179</v>
@@ -3709,7 +3721,7 @@
         <v>64</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>64</v>
@@ -3729,31 +3741,31 @@
         <v>78</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J46" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3761,31 +3773,31 @@
         <v>78</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J47" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3793,31 +3805,31 @@
         <v>78</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J48" s="7" t="s">
         <v>187</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3825,19 +3837,19 @@
         <v>78</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="E49" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>64</v>
@@ -3857,19 +3869,19 @@
         <v>78</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>64</v>
@@ -3892,28 +3904,28 @@
         <v>193</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J51" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3921,13 +3933,13 @@
         <v>78</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>64</v>
@@ -3945,7 +3957,7 @@
         <v>64</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3953,19 +3965,19 @@
         <v>78</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D53" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>64</v>
@@ -3980,55 +3992,125 @@
         <v>199</v>
       </c>
     </row>
+    <row r="54" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="16">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G13">
+  <dataValidations count="18">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G10:G11">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G14:G23">
-      <formula1>Listas!$E$2:$E$9</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G12">
+      <formula1>Listas!$E$2:$E$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G13:G15">
+      <formula1>Listas!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G16:G25">
+      <formula1>Listas!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G29:G31">
-      <formula1>Listas!$D$2:$D$3</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G3:G4">
       <formula1>Listas!$B$2:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G32">
-      <formula1>Listas!$F$2:$F$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G33:G35">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G31:G33">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G36:G45">
-      <formula1>Listas!$E$2:$E$9</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G34">
+      <formula1>Listas!$E$2:$E$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G46">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G35:G37">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G47:G48">
-      <formula1>Listas!$E$2:$E$9</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G38:G47">
+      <formula1>Listas!$F$2:$F$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G49">
-      <formula1>Listas!$F$2:$F$21</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G48">
+      <formula1>Listas!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G49:G50">
+      <formula1>Listas!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5">
       <formula1>Listas!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G50">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G51">
+      <formula1>Listas!$E$2:$E$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G52">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G51">
-      <formula1>Listas!$F$2:$F$21</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G53">
+      <formula1>Listas!$E$2:$E$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G52:G53">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G54:G55">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G6:G13">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G6:G11">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -4061,19 +4143,19 @@
         <v>52</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>58</v>
@@ -4084,19 +4166,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>64</v>
@@ -4108,7 +4190,7 @@
         <v>64</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4119,13 +4201,13 @@
         <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>64</v>
@@ -4137,24 +4219,24 @@
         <v>64</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>64</v>
@@ -4166,24 +4248,24 @@
         <v>64</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>64</v>
@@ -4195,24 +4277,24 @@
         <v>64</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>64</v>
@@ -4224,7 +4306,7 @@
         <v>64</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4235,13 +4317,13 @@
         <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>64</v>
@@ -4253,24 +4335,24 @@
         <v>64</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>64</v>
@@ -4282,24 +4364,24 @@
         <v>64</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>64</v>
@@ -4311,24 +4393,24 @@
         <v>64</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>64</v>
@@ -4340,24 +4422,24 @@
         <v>64</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>64</v>
@@ -4369,24 +4451,24 @@
         <v>64</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>64</v>
@@ -4398,24 +4480,24 @@
         <v>64</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>64</v>
@@ -4427,24 +4509,24 @@
         <v>64</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>64</v>
@@ -4456,24 +4538,24 @@
         <v>64</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>64</v>
@@ -4485,24 +4567,24 @@
         <v>64</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>64</v>
@@ -4514,7 +4596,7 @@
         <v>64</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -4557,22 +4639,22 @@
         <v>51</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>58</v>
@@ -4583,22 +4665,22 @@
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>64</v>
@@ -4610,27 +4692,27 @@
         <v>64</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>64</v>
@@ -4642,27 +4724,27 @@
         <v>64</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>264</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>64</v>
@@ -4674,27 +4756,27 @@
         <v>64</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>64</v>
@@ -4706,27 +4788,27 @@
         <v>64</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>64</v>
@@ -4738,27 +4820,27 @@
         <v>64</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>64</v>
@@ -4770,27 +4852,27 @@
         <v>64</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>64</v>
@@ -4802,28 +4884,28 @@
         <v>64</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="G9" s="8" t="s">
         <v>64</v>
       </c>
@@ -4834,27 +4916,27 @@
         <v>64</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>64</v>
@@ -4866,27 +4948,27 @@
         <v>64</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>64</v>
@@ -4898,27 +4980,27 @@
         <v>64</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>64</v>
@@ -4930,27 +5012,27 @@
         <v>64</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>64</v>
@@ -4962,27 +5044,27 @@
         <v>64</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>64</v>
@@ -4994,27 +5076,27 @@
         <v>64</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>64</v>
@@ -5026,27 +5108,27 @@
         <v>64</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>64</v>
@@ -5058,27 +5140,27 @@
         <v>64</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>64</v>
@@ -5090,27 +5172,27 @@
         <v>64</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>64</v>
@@ -5122,27 +5204,27 @@
         <v>64</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>64</v>
@@ -5154,27 +5236,27 @@
         <v>64</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>64</v>
@@ -5186,27 +5268,27 @@
         <v>64</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>64</v>
@@ -5218,27 +5300,27 @@
         <v>64</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>64</v>
@@ -5250,27 +5332,27 @@
         <v>64</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>64</v>
@@ -5282,27 +5364,27 @@
         <v>64</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>64</v>
@@ -5314,27 +5396,27 @@
         <v>64</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>64</v>
@@ -5346,27 +5428,27 @@
         <v>64</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>64</v>
@@ -5378,27 +5460,27 @@
         <v>64</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>64</v>
@@ -5410,27 +5492,27 @@
         <v>64</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>64</v>
@@ -5442,27 +5524,27 @@
         <v>64</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>64</v>
@@ -5474,27 +5556,27 @@
         <v>64</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>64</v>
@@ -5506,27 +5588,27 @@
         <v>64</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>64</v>
@@ -5538,27 +5620,27 @@
         <v>64</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>64</v>
@@ -5570,27 +5652,27 @@
         <v>64</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>64</v>
@@ -5602,27 +5684,27 @@
         <v>64</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>64</v>
@@ -5634,27 +5716,27 @@
         <v>64</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>64</v>
@@ -5666,28 +5748,28 @@
         <v>64</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="G36" s="8" t="s">
         <v>64</v>
       </c>
@@ -5698,27 +5780,27 @@
         <v>64</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>64</v>
@@ -5730,28 +5812,28 @@
         <v>64</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="G38" s="8" t="s">
         <v>64</v>
       </c>
@@ -5762,28 +5844,28 @@
         <v>64</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="G39" s="8" t="s">
         <v>64</v>
       </c>
@@ -5794,27 +5876,27 @@
         <v>64</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>64</v>
@@ -5826,28 +5908,28 @@
         <v>64</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="G41" s="8" t="s">
         <v>64</v>
       </c>
@@ -5858,27 +5940,27 @@
         <v>64</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>64</v>
@@ -5890,27 +5972,27 @@
         <v>64</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>64</v>
@@ -5922,27 +6004,27 @@
         <v>64</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>64</v>
@@ -5954,27 +6036,27 @@
         <v>64</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>64</v>
@@ -5986,27 +6068,27 @@
         <v>64</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>64</v>
@@ -6018,27 +6100,27 @@
         <v>64</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>64</v>
@@ -6050,27 +6132,27 @@
         <v>64</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>64</v>
@@ -6082,27 +6164,27 @@
         <v>64</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>64</v>
@@ -6114,27 +6196,27 @@
         <v>64</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>64</v>
@@ -6146,27 +6228,27 @@
         <v>64</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>64</v>
@@ -6178,27 +6260,27 @@
         <v>64</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>64</v>
@@ -6210,27 +6292,27 @@
         <v>64</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>64</v>
@@ -6242,7 +6324,7 @@
         <v>64</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -6280,37 +6362,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>54</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6318,34 +6400,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C2" s="3">
         <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6359,28 +6441,28 @@
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6388,34 +6470,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C4" s="3">
         <v>108</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6429,28 +6511,28 @@
         <v>225</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6464,28 +6546,28 @@
         <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>451</v>
-      </c>
       <c r="K6" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6493,34 +6575,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C7" s="3">
         <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6528,34 +6610,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C8" s="3">
         <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6563,34 +6645,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C9" s="3">
         <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6598,34 +6680,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3">
         <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6633,34 +6715,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C11" s="3">
         <v>38</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6668,34 +6750,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C12" s="3">
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6703,34 +6785,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C13" s="3">
         <v>84</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6738,34 +6820,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C14" s="3">
         <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6779,28 +6861,28 @@
         <v>99</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6814,28 +6896,28 @@
         <v>2</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6843,34 +6925,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C17" s="3">
         <v>148</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6878,34 +6960,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C18" s="3">
         <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6913,34 +6995,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C19" s="3">
         <v>8</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="I19" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6948,34 +7030,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C20" s="3">
         <v>5</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6983,34 +7065,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C21" s="3">
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7018,34 +7100,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C22" s="3">
         <v>50</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>476</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7053,34 +7135,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C23" s="3">
         <v>88</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7088,34 +7170,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C24" s="3">
         <v>82</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7123,34 +7205,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C25" s="3">
         <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7158,34 +7240,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C26" s="3">
         <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7193,34 +7275,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C27" s="3">
         <v>88</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7228,34 +7310,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3">
         <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7263,34 +7345,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3">
         <v>50</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7298,34 +7380,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C30" s="3">
         <v>68</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="I30" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7333,34 +7415,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C31" s="3">
         <v>86</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7368,34 +7450,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C32" s="3">
         <v>200</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7403,34 +7485,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C33" s="3">
         <v>64</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7438,34 +7520,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C34" s="3">
         <v>100</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="I34" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7473,34 +7555,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C35" s="3">
         <v>50</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7508,34 +7590,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C36" s="3">
         <v>24</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7543,34 +7625,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C37" s="3">
         <v>52</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7578,34 +7660,34 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C38" s="3">
         <v>40</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7613,34 +7695,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C39" s="3">
         <v>20</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7648,34 +7730,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C40" s="3">
         <v>10</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7683,34 +7765,34 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3">
         <v>4</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7718,34 +7800,34 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C42" s="3">
         <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I42" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7753,34 +7835,34 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C43" s="3">
         <v>7</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7788,34 +7870,34 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C44" s="3">
         <v>24</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I44" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7823,34 +7905,34 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C45" s="3">
         <v>92</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7858,34 +7940,34 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C46" s="3">
         <v>80</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="I46" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7893,34 +7975,34 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C47" s="3">
         <v>144</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="471">
   <si>
     <t>Migración métrica · El caballero de Olmedo</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -261,7 +261,7 @@
     <t>Esquema de rima · 11 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta)</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
   </si>
   <si>
     <t>R|e5e17fde-27d6-462e-a566-93a08eda12b1|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -270,7 +270,7 @@
     <t>Esquema de rima · todas las estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones» (versos: respuesta). Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
   </si>
   <si>
     <t>R|8b0e77d1-19b4-492a-a7b4-46380f9e0a9e|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -354,97 +354,25 @@
     <t>Copla real · Octosílaba consonante</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · copla real 1 (vv. 1113–1122)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1113</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · copla real 2 (vv. 1123–1132)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1123</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · copla real 3 (vv. 1133–1142)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1133</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · copla real 4 (vv. 1143–1152)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1143</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · copla real 5 (vv. 1153–1162)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc|1153</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 1 (vv. 1113–1122)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1113</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 2 (vv. 1123–1132)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1123</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 3 (vv. 1133–1142)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1133</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 4 (vv. 1143–1152)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1143</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 5 (vv. 1153–1162)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a|1153</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 1 (vv. 1113–1122)</t>
-  </si>
-  <si>
-    <t>Indica en qué versos cae el quebrado y cuántas sílabas tiene cada uno («3: 4, 8: 5»)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1113</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 2 (vv. 1123–1132)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1123</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 3 (vv. 1133–1142)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1133</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 4 (vv. 1143–1152)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1143</t>
-  </si>
-  <si>
-    <t>Pie quebrado · estrofa 5 (vv. 1153–1162)</t>
-  </si>
-  <si>
-    <t>U|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7|1153</t>
+    <t>Primera quintilla · Esquema de rima · 5 estrofas</t>
+  </si>
+  <si>
+    <t>R|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|7d6da838-573a-4d7f-a38b-ddcff61173cc</t>
+  </si>
+  <si>
+    <t>Segunda quintilla · Esquema de rima · 5 estrofas</t>
+  </si>
+  <si>
+    <t>R|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|73d6744a-81e5-478f-8b98-0444f007919a</t>
+  </si>
+  <si>
+    <t>Pie quebrado · 5 estrofas</t>
+  </si>
+  <si>
+    <t>Indica en qué versos cae el quebrado y cuántas sílabas tiene cada uno («3: 4, 8: 5»). La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «568-575: 7 11 7 7 11»</t>
+  </si>
+  <si>
+    <t>R|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7</t>
   </si>
   <si>
     <t>1163–1250</t>
@@ -513,64 +441,10 @@
     <t>2178–2227</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · copla real 1 (vv. 2178–2187)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2178</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · copla real 2 (vv. 2188–2197)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2188</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · copla real 3 (vv. 2198–2207)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2198</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · copla real 4 (vv. 2208–2217)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2208</t>
-  </si>
-  <si>
-    <t>Primera quintilla · Esquema de rima · copla real 5 (vv. 2218–2227)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc|2218</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 1 (vv. 2178–2187)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2178</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 2 (vv. 2188–2197)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2188</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 3 (vv. 2198–2207)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2198</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 4 (vv. 2208–2217)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2208</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 5 (vv. 2218–2227)</t>
-  </si>
-  <si>
-    <t>U|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a|2218</t>
+    <t>R|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|7d6da838-573a-4d7f-a38b-ddcff61173cc</t>
+  </si>
+  <si>
+    <t>R|856f04c9-3fe6-4c2e-bd40-a961a1b3cab7|73d6744a-81e5-478f-8b98-0444f007919a</t>
   </si>
   <si>
     <t>2228–2251</t>
@@ -585,16 +459,16 @@
     <t>2364–2373</t>
   </si>
   <si>
-    <t>Primera quintilla · Esquema de rima · copla real 1 (vv. 2364–2373)</t>
-  </si>
-  <si>
-    <t>U|233c1cc1-8d46-4486-b32d-3c9cb395e604|7d6da838-573a-4d7f-a38b-ddcff61173cc|2364</t>
-  </si>
-  <si>
-    <t>Segunda quintilla · Esquema de rima · copla real 1 (vv. 2364–2373)</t>
-  </si>
-  <si>
-    <t>U|233c1cc1-8d46-4486-b32d-3c9cb395e604|73d6744a-81e5-478f-8b98-0444f007919a|2364</t>
+    <t>Primera quintilla · Esquema de rima · 1 estrofa</t>
+  </si>
+  <si>
+    <t>R|233c1cc1-8d46-4486-b32d-3c9cb395e604|7d6da838-573a-4d7f-a38b-ddcff61173cc</t>
+  </si>
+  <si>
+    <t>Segunda quintilla · Esquema de rima · 1 estrofa</t>
+  </si>
+  <si>
+    <t>R|233c1cc1-8d46-4486-b32d-3c9cb395e604|73d6744a-81e5-478f-8b98-0444f007919a</t>
   </si>
   <si>
     <t>2374–2377</t>
@@ -2282,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -2793,7 +2667,7 @@
         <v>64</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>64</v>
@@ -2825,7 +2699,7 @@
         <v>64</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>64</v>
@@ -2857,7 +2731,7 @@
         <v>64</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>64</v>
@@ -2869,7 +2743,7 @@
         <v>64</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2877,19 +2751,19 @@
         <v>78</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>64</v>
@@ -2901,7 +2775,7 @@
         <v>64</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2909,19 +2783,19 @@
         <v>78</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>64</v>
@@ -2933,7 +2807,7 @@
         <v>64</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2941,19 +2815,19 @@
         <v>78</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>64</v>
@@ -2965,7 +2839,7 @@
         <v>64</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2973,13 +2847,13 @@
         <v>78</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>64</v>
@@ -2997,7 +2871,7 @@
         <v>64</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3005,19 +2879,19 @@
         <v>78</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>64</v>
@@ -3029,7 +2903,7 @@
         <v>64</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3037,19 +2911,19 @@
         <v>78</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>64</v>
@@ -3061,7 +2935,7 @@
         <v>64</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3069,19 +2943,19 @@
         <v>78</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>64</v>
@@ -3093,7 +2967,7 @@
         <v>64</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3101,19 +2975,19 @@
         <v>78</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>64</v>
@@ -3125,7 +2999,7 @@
         <v>64</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3133,19 +3007,19 @@
         <v>78</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>64</v>
@@ -3157,7 +3031,7 @@
         <v>64</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3165,19 +3039,19 @@
         <v>78</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>64</v>
@@ -3189,7 +3063,7 @@
         <v>64</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3197,19 +3071,19 @@
         <v>78</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>64</v>
@@ -3221,7 +3095,7 @@
         <v>64</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3229,19 +3103,19 @@
         <v>78</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>64</v>
@@ -3253,7 +3127,7 @@
         <v>64</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3261,19 +3135,19 @@
         <v>78</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>64</v>
@@ -3285,7 +3159,7 @@
         <v>64</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3293,13 +3167,13 @@
         <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>64</v>
@@ -3317,7 +3191,7 @@
         <v>64</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3325,19 +3199,19 @@
         <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>64</v>
@@ -3349,7 +3223,7 @@
         <v>64</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3357,19 +3231,19 @@
         <v>78</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>98</v>
+        <v>144</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>64</v>
@@ -3381,7 +3255,7 @@
         <v>64</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3389,13 +3263,13 @@
         <v>78</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>64</v>
@@ -3413,647 +3287,7 @@
         <v>64</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4068,47 +3302,47 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G13:G15">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G16:G25">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G16:G17">
       <formula1>Listas!$F$2:$F$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G19:G21">
+      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G2">
       <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G22">
+      <formula1>Listas!$E$2:$E$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G23:G25">
+      <formula1>Listas!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G26:G27">
+      <formula1>Listas!$F$2:$F$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G28">
+      <formula1>Listas!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G29:G30">
+      <formula1>Listas!$F$2:$F$9</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G3:G4">
       <formula1>Listas!$B$2:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G31:G33">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G31">
+      <formula1>Listas!$E$2:$E$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G32">
       <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G34">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G33">
       <formula1>Listas!$E$2:$E$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G35:G37">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G34:G35">
       <formula1>Listas!$D$2:$D$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G38:G47">
-      <formula1>Listas!$F$2:$F$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G48">
-      <formula1>Listas!$D$2:$D$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G49:G50">
-      <formula1>Listas!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G5">
       <formula1>Listas!$C$2:$C$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G51">
-      <formula1>Listas!$E$2:$E$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G52">
-      <formula1>Listas!$D$2:$D$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G53">
-      <formula1>Listas!$E$2:$E$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G54:G55">
-      <formula1>Listas!$D$2:$D$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G6:G11">
       <formula1>Listas!$D$2:$D$3</formula1>
@@ -4143,19 +3377,19 @@
         <v>52</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>58</v>
@@ -4166,7 +3400,7 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>68</v>
@@ -4178,7 +3412,7 @@
         <v>39</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>64</v>
@@ -4190,7 +3424,7 @@
         <v>64</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4207,7 +3441,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>64</v>
@@ -4219,24 +3453,24 @@
         <v>64</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>212</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>64</v>
@@ -4248,12 +3482,12 @@
         <v>64</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>218</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>68</v>
@@ -4265,7 +3499,7 @@
         <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>64</v>
@@ -4277,12 +3511,12 @@
         <v>64</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>221</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>68</v>
@@ -4294,7 +3528,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>64</v>
@@ -4306,7 +3540,7 @@
         <v>64</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>223</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4323,7 +3557,7 @@
         <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>64</v>
@@ -4335,12 +3569,12 @@
         <v>64</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>68</v>
@@ -4352,7 +3586,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>64</v>
@@ -4364,24 +3598,24 @@
         <v>64</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>228</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>64</v>
@@ -4393,12 +3627,12 @@
         <v>64</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>234</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>68</v>
@@ -4410,7 +3644,7 @@
         <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>64</v>
@@ -4422,12 +3656,12 @@
         <v>64</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>68</v>
@@ -4439,7 +3673,7 @@
         <v>22</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>64</v>
@@ -4451,12 +3685,12 @@
         <v>64</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>68</v>
@@ -4468,7 +3702,7 @@
         <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>64</v>
@@ -4480,12 +3714,12 @@
         <v>64</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>241</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>68</v>
@@ -4497,7 +3731,7 @@
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>64</v>
@@ -4509,24 +3743,24 @@
         <v>64</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>64</v>
@@ -4538,12 +3772,12 @@
         <v>64</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>68</v>
@@ -4555,7 +3789,7 @@
         <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>64</v>
@@ -4567,12 +3801,12 @@
         <v>64</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>68</v>
@@ -4584,7 +3818,7 @@
         <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>64</v>
@@ -4596,7 +3830,7 @@
         <v>64</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>254</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4639,22 +3873,22 @@
         <v>51</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>258</v>
+        <v>216</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>58</v>
@@ -4665,22 +3899,22 @@
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>64</v>
@@ -4692,27 +3926,27 @@
         <v>64</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>269</v>
+        <v>227</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>64</v>
@@ -4724,27 +3958,27 @@
         <v>64</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>271</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>272</v>
+        <v>230</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>64</v>
@@ -4756,27 +3990,27 @@
         <v>64</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>274</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>64</v>
@@ -4788,27 +4022,27 @@
         <v>64</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>277</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>64</v>
@@ -4820,27 +4054,27 @@
         <v>64</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>280</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>282</v>
+        <v>240</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>64</v>
@@ -4852,27 +4086,27 @@
         <v>64</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>290</v>
+        <v>248</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>64</v>
@@ -4884,27 +4118,27 @@
         <v>64</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>64</v>
@@ -4916,27 +4150,27 @@
         <v>64</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>297</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>64</v>
@@ -4948,27 +4182,27 @@
         <v>64</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>301</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>64</v>
@@ -4980,27 +4214,27 @@
         <v>64</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>64</v>
@@ -5012,27 +4246,27 @@
         <v>64</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>310</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>64</v>
@@ -5044,27 +4278,27 @@
         <v>64</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>64</v>
@@ -5076,27 +4310,27 @@
         <v>64</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>315</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>64</v>
@@ -5108,27 +4342,27 @@
         <v>64</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>64</v>
@@ -5140,27 +4374,27 @@
         <v>64</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>321</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>64</v>
@@ -5172,27 +4406,27 @@
         <v>64</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>324</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>327</v>
+        <v>285</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>64</v>
@@ -5204,27 +4438,27 @@
         <v>64</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>328</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>64</v>
@@ -5236,27 +4470,27 @@
         <v>64</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>331</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>332</v>
+        <v>290</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>333</v>
+        <v>291</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>334</v>
+        <v>292</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>64</v>
@@ -5268,27 +4502,27 @@
         <v>64</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>335</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>336</v>
+        <v>294</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>337</v>
+        <v>295</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>64</v>
@@ -5300,27 +4534,27 @@
         <v>64</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>340</v>
+        <v>298</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>342</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>64</v>
@@ -5332,27 +4566,27 @@
         <v>64</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>343</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>345</v>
+        <v>303</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>290</v>
+        <v>248</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>346</v>
+        <v>304</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>64</v>
@@ -5364,27 +4598,27 @@
         <v>64</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>347</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>348</v>
+        <v>306</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>349</v>
+        <v>307</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>350</v>
+        <v>308</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>64</v>
@@ -5396,27 +4630,27 @@
         <v>64</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>352</v>
+        <v>310</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>349</v>
+        <v>307</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>353</v>
+        <v>311</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>64</v>
@@ -5428,27 +4662,27 @@
         <v>64</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>355</v>
+        <v>313</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>349</v>
+        <v>307</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>356</v>
+        <v>314</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>64</v>
@@ -5460,27 +4694,27 @@
         <v>64</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>357</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>359</v>
+        <v>317</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>64</v>
@@ -5492,27 +4726,27 @@
         <v>64</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>361</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>362</v>
+        <v>320</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>363</v>
+        <v>321</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>364</v>
+        <v>322</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>64</v>
@@ -5524,27 +4758,27 @@
         <v>64</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>365</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>363</v>
+        <v>321</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>367</v>
+        <v>325</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>64</v>
@@ -5556,27 +4790,27 @@
         <v>64</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>368</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>363</v>
+        <v>321</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>370</v>
+        <v>328</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>64</v>
@@ -5588,27 +4822,27 @@
         <v>64</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>372</v>
+        <v>330</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>64</v>
@@ -5620,27 +4854,27 @@
         <v>64</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>374</v>
+        <v>332</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>375</v>
+        <v>333</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>64</v>
@@ -5652,27 +4886,27 @@
         <v>64</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>379</v>
+        <v>337</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>380</v>
+        <v>338</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>64</v>
@@ -5684,27 +4918,27 @@
         <v>64</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>381</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>382</v>
+        <v>340</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>383</v>
+        <v>341</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>64</v>
@@ -5716,27 +4950,27 @@
         <v>64</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>384</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>385</v>
+        <v>343</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>386</v>
+        <v>344</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>387</v>
+        <v>345</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>64</v>
@@ -5748,27 +4982,27 @@
         <v>64</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>389</v>
+        <v>347</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>64</v>
@@ -5780,27 +5014,27 @@
         <v>64</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>392</v>
+        <v>350</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>393</v>
+        <v>351</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>64</v>
@@ -5812,27 +5046,27 @@
         <v>64</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>394</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>395</v>
+        <v>353</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>64</v>
@@ -5844,27 +5078,27 @@
         <v>64</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>396</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>397</v>
+        <v>355</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>64</v>
@@ -5876,27 +5110,27 @@
         <v>64</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>398</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>399</v>
+        <v>357</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>400</v>
+        <v>358</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>64</v>
@@ -5908,27 +5142,27 @@
         <v>64</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>401</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>402</v>
+        <v>360</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>64</v>
@@ -5940,27 +5174,27 @@
         <v>64</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>403</v>
+        <v>361</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>404</v>
+        <v>362</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>405</v>
+        <v>363</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>406</v>
+        <v>364</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>64</v>
@@ -5972,27 +5206,27 @@
         <v>64</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>407</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>408</v>
+        <v>366</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>405</v>
+        <v>363</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>409</v>
+        <v>367</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>64</v>
@@ -6004,27 +5238,27 @@
         <v>64</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>410</v>
+        <v>368</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>412</v>
+        <v>370</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>64</v>
@@ -6036,27 +5270,27 @@
         <v>64</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>413</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>414</v>
+        <v>372</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>415</v>
+        <v>373</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>64</v>
@@ -6068,27 +5302,27 @@
         <v>64</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>416</v>
+        <v>374</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>417</v>
+        <v>375</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>418</v>
+        <v>376</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>264</v>
+        <v>222</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>64</v>
@@ -6100,27 +5334,27 @@
         <v>64</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>419</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>420</v>
+        <v>378</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>418</v>
+        <v>376</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>64</v>
@@ -6132,27 +5366,27 @@
         <v>64</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>421</v>
+        <v>379</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>422</v>
+        <v>380</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>64</v>
@@ -6164,27 +5398,27 @@
         <v>64</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>423</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>424</v>
+        <v>382</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>292</v>
+        <v>250</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>64</v>
@@ -6196,27 +5430,27 @@
         <v>64</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>64</v>
@@ -6228,27 +5462,27 @@
         <v>64</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>428</v>
+        <v>386</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>429</v>
+        <v>387</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>427</v>
+        <v>385</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>64</v>
@@ -6260,27 +5494,27 @@
         <v>64</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>430</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>431</v>
+        <v>389</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>432</v>
+        <v>390</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>64</v>
@@ -6292,27 +5526,27 @@
         <v>64</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>433</v>
+        <v>391</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>260</v>
+        <v>218</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>434</v>
+        <v>392</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>432</v>
+        <v>390</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>268</v>
+        <v>226</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>64</v>
@@ -6324,7 +5558,7 @@
         <v>64</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>435</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -6362,37 +5596,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>436</v>
+        <v>394</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>437</v>
+        <v>395</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>438</v>
+        <v>396</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>439</v>
+        <v>397</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>440</v>
+        <v>398</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>441</v>
+        <v>399</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>54</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>442</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6400,34 +5634,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>443</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3">
         <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>444</v>
+        <v>402</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>445</v>
+        <v>403</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6441,28 +5675,28 @@
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6470,34 +5704,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>208</v>
+        <v>166</v>
       </c>
       <c r="C4" s="3">
         <v>108</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>454</v>
+        <v>412</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6511,28 +5745,28 @@
         <v>225</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>457</v>
+        <v>415</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>458</v>
+        <v>416</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6546,28 +5780,28 @@
         <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>459</v>
+        <v>417</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6575,34 +5809,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>460</v>
+        <v>418</v>
       </c>
       <c r="C7" s="3">
         <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>444</v>
+        <v>402</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>445</v>
+        <v>403</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>461</v>
+        <v>419</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6616,28 +5850,28 @@
         <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6645,34 +5879,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="C9" s="3">
         <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>290</v>
+        <v>248</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6686,28 +5920,28 @@
         <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6715,34 +5949,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="C11" s="3">
         <v>38</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>220</v>
+        <v>178</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6756,28 +5990,28 @@
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6785,34 +6019,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="C13" s="3">
         <v>84</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>466</v>
+        <v>424</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6826,28 +6060,28 @@
         <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>467</v>
+        <v>425</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6861,28 +6095,28 @@
         <v>99</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>469</v>
+        <v>427</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6896,28 +6130,28 @@
         <v>2</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>470</v>
+        <v>428</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>471</v>
+        <v>429</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>473</v>
+        <v>431</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6931,28 +6165,28 @@
         <v>148</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>474</v>
+        <v>432</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6960,34 +6194,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>475</v>
+        <v>433</v>
       </c>
       <c r="C18" s="3">
         <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>444</v>
+        <v>402</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>445</v>
+        <v>403</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>476</v>
+        <v>434</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7001,28 +6235,28 @@
         <v>8</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>477</v>
+        <v>435</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7030,34 +6264,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C20" s="3">
         <v>5</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>478</v>
+        <v>436</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>481</v>
+        <v>439</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>290</v>
+        <v>248</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>482</v>
+        <v>440</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>483</v>
+        <v>441</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7071,28 +6305,28 @@
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7106,28 +6340,28 @@
         <v>50</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>484</v>
+        <v>442</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>487</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7135,34 +6369,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="C23" s="3">
         <v>88</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>488</v>
+        <v>446</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7170,34 +6404,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="C24" s="3">
         <v>82</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>489</v>
+        <v>447</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7205,34 +6439,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="C25" s="3">
         <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>491</v>
+        <v>449</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>492</v>
+        <v>450</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7240,34 +6474,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3">
         <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>493</v>
+        <v>451</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7275,34 +6509,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="C27" s="3">
         <v>88</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>494</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7310,34 +6544,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="C28" s="3">
         <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7345,34 +6579,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="C29" s="3">
         <v>50</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>495</v>
+        <v>453</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>498</v>
+        <v>456</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>499</v>
+        <v>457</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7380,34 +6614,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="C30" s="3">
         <v>68</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>500</v>
+        <v>458</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7415,34 +6649,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="C31" s="3">
         <v>86</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>501</v>
+        <v>459</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7450,34 +6684,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C32" s="3">
         <v>200</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>502</v>
+        <v>460</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7485,34 +6719,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="C33" s="3">
         <v>64</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7520,34 +6754,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="C34" s="3">
         <v>100</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>503</v>
+        <v>461</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7555,34 +6789,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C35" s="3">
         <v>50</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>504</v>
+        <v>462</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7590,34 +6824,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="C36" s="3">
         <v>24</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>505</v>
+        <v>463</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7625,34 +6859,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="C37" s="3">
         <v>52</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>243</v>
+        <v>201</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7660,34 +6894,34 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="C38" s="3">
         <v>40</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>249</v>
+        <v>207</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>507</v>
+        <v>465</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>508</v>
+        <v>466</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7695,34 +6929,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>509</v>
+        <v>467</v>
       </c>
       <c r="C39" s="3">
         <v>20</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>444</v>
+        <v>402</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>445</v>
+        <v>403</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7730,34 +6964,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="C40" s="3">
         <v>10</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>504</v>
+        <v>462</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>485</v>
+        <v>443</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7765,34 +6999,34 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="C41" s="3">
         <v>4</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>470</v>
+        <v>428</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>471</v>
+        <v>429</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>499</v>
+        <v>457</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7800,34 +7034,34 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="C42" s="3">
         <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7835,34 +7069,34 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>197</v>
+        <v>155</v>
       </c>
       <c r="C43" s="3">
         <v>7</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>470</v>
+        <v>428</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>471</v>
+        <v>429</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>510</v>
+        <v>468</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>499</v>
+        <v>457</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7870,34 +7104,34 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="C44" s="3">
         <v>24</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7905,34 +7139,34 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3">
         <v>92</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7940,34 +7174,34 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="C46" s="3">
         <v>80</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>511</v>
+        <v>469</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>447</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7975,34 +7209,34 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="C47" s="3">
         <v>144</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>452</v>
+        <v>410</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>453</v>
+        <v>411</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>512</v>
+        <v>470</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>456</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/el-caballero-de-olmedo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="466">
   <si>
     <t>Migración métrica · El caballero de Olmedo</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -42,21 +42,6 @@
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
-  </si>
-  <si>
     <t>lista</t>
   </si>
   <si>
@@ -261,7 +246,7 @@
     <t>Esquema de rima · 11 estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab»</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab»</t>
   </si>
   <si>
     <t>R|e5e17fde-27d6-462e-a566-93a08eda12b1|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -270,7 +255,7 @@
     <t>Esquema de rima · todas las estrofas</t>
   </si>
   <si>
-    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «191-194: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
+    <t>Elige en el desplegable. La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «191-194: abab; 203-206: abab». Cuántas estrofas son depende de lo que decidas arriba, así que contéstalo para todas</t>
   </si>
   <si>
     <t>R|8b0e77d1-19b4-492a-a7b4-46380f9e0a9e|b4bad32a-b9ac-4304-9003-e8af28ecc3f0</t>
@@ -369,7 +354,7 @@
     <t>Pie quebrado · 5 estrofas</t>
   </si>
   <si>
-    <t>Indica en qué versos cae el quebrado y cuántas sílabas tiene cada uno («3: 4, 8: 5»). La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», como «568-575: 7 11 7 7 11»</t>
+    <t>Indica en qué versos cae el quebrado y cuántas sílabas tiene cada uno («3: 4, 8: 5»). La respuesta vale para todas las estrofas; las que sean distintas, en «Excepciones», una detrás de otra y separadas por punto y coma, como «568-575: 7 11 7 7 11; 592-599: 7 7 11 11 7»</t>
   </si>
   <si>
     <t>R|a6e59887-ccc7-4e7f-99b3-a492f1359a4f|58a8be4c-94e0-4c59-89ca-db8e56158cb7</t>
@@ -1518,14 +1503,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1877,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -1921,31 +1905,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1964,188 +1923,188 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E21" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2170,1124 +2129,1124 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="G4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>77</v>
+      <c r="G5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>88</v>
+        <v>76</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>91</v>
+        <v>76</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>94</v>
+        <v>76</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>97</v>
+        <v>76</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>103</v>
+        <v>76</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>106</v>
+        <v>76</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>109</v>
+        <v>94</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>113</v>
+        <v>76</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>121</v>
+        <v>76</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>124</v>
+        <v>76</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>127</v>
+        <v>76</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>130</v>
+        <v>94</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>133</v>
+        <v>76</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>136</v>
+        <v>76</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>139</v>
+        <v>76</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>141</v>
+        <v>76</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>142</v>
+        <v>76</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>145</v>
+        <v>76</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>148</v>
+        <v>94</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>150</v>
+        <v>94</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>152</v>
+        <v>94</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>154</v>
+        <v>76</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>157</v>
+        <v>94</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>159</v>
+        <v>76</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>161</v>
+        <v>76</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3369,468 +3328,468 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>59</v>
+      <c r="E1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>170</v>
+        <v>164</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>179</v>
+        <v>173</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>181</v>
+        <v>164</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>183</v>
+        <v>177</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>186</v>
+        <v>180</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>194</v>
+        <v>177</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>196</v>
+        <v>164</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>199</v>
+        <v>193</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>202</v>
+        <v>196</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>210</v>
+        <v>177</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>212</v>
+        <v>177</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -3865,1700 +3824,1700 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>59</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>232</v>
+        <v>223</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>235</v>
+        <v>223</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>238</v>
+        <v>217</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="G7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>246</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>259</v>
+        <v>223</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>266</v>
+        <v>223</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>273</v>
+      <c r="G14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>271</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>279</v>
+        <v>217</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>282</v>
+        <v>223</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>286</v>
+        <v>217</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>293</v>
+        <v>287</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>297</v>
+        <v>223</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>301</v>
+        <v>217</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>305</v>
+        <v>245</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>309</v>
+        <v>223</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>315</v>
+        <v>223</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>319</v>
+        <v>217</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>323</v>
+        <v>223</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>329</v>
+        <v>217</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>332</v>
+        <v>223</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>336</v>
+        <v>245</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>334</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>342</v>
+        <v>223</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>346</v>
+        <v>223</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>349</v>
+        <v>245</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>352</v>
+        <v>217</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>354</v>
+        <v>245</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>356</v>
+        <v>245</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>359</v>
+        <v>217</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>361</v>
+        <v>245</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>365</v>
+      <c r="G42" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>363</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>371</v>
+        <v>217</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>374</v>
+        <v>223</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>377</v>
+        <v>217</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>379</v>
+        <v>223</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>381</v>
+        <v>245</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>383</v>
+        <v>245</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>386</v>
+        <v>223</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>388</v>
+        <v>223</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>391</v>
+        <v>223</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>393</v>
+        <v>223</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -5594,39 +5553,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5634,34 +5593,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C2" s="3">
         <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5669,34 +5628,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
         <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5704,34 +5663,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C4" s="3">
         <v>108</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5739,34 +5698,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C5" s="3">
         <v>225</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5774,34 +5733,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C6" s="3">
         <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5809,34 +5768,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C7" s="3">
         <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5844,34 +5803,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3">
         <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5879,34 +5838,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C9" s="3">
         <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5914,34 +5873,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C10" s="3">
         <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5949,34 +5908,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C11" s="3">
         <v>38</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5984,34 +5943,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C12" s="3">
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6019,34 +5978,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C13" s="3">
         <v>84</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6054,34 +6013,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C14" s="3">
         <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6089,34 +6048,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3">
         <v>99</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6124,34 +6083,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C16" s="3">
         <v>2</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6159,34 +6118,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C17" s="3">
         <v>148</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6194,34 +6153,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C18" s="3">
         <v>60</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6229,34 +6188,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C19" s="3">
         <v>8</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6264,34 +6223,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C20" s="3">
         <v>5</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>441</v>
-      </c>
       <c r="K20" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6299,34 +6258,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C21" s="3">
         <v>4</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6334,34 +6293,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C22" s="3">
         <v>50</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6369,34 +6328,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3">
         <v>88</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6404,34 +6363,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C24" s="3">
         <v>82</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6439,34 +6398,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C25" s="3">
         <v>61</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6474,34 +6433,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C26" s="3">
         <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6509,34 +6468,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C27" s="3">
         <v>88</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6544,34 +6503,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C28" s="3">
         <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6579,34 +6538,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C29" s="3">
         <v>50</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6614,34 +6573,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C30" s="3">
         <v>68</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6649,34 +6608,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C31" s="3">
         <v>86</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6684,34 +6643,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C32" s="3">
         <v>200</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6719,34 +6678,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C33" s="3">
         <v>64</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6754,34 +6713,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C34" s="3">
         <v>100</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6789,34 +6748,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C35" s="3">
         <v>50</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6824,34 +6783,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C36" s="3">
         <v>24</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6859,34 +6818,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C37" s="3">
         <v>52</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="38" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6894,34 +6853,34 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C38" s="3">
         <v>40</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6929,34 +6888,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C39" s="3">
         <v>20</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6964,34 +6923,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C40" s="3">
         <v>10</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6999,34 +6958,34 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C41" s="3">
         <v>4</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7034,34 +6993,34 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C42" s="3">
         <v>8</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7069,34 +7028,34 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C43" s="3">
         <v>7</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7104,34 +7063,34 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C44" s="3">
         <v>24</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7139,34 +7098,34 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3">
         <v>92</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7174,34 +7133,34 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C46" s="3">
         <v>80</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7209,34 +7168,34 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C47" s="3">
         <v>144</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
